--- a/output/Campus FY 2025-26 annual statistics NZ-level report/2025 - 2026/exclusions tab/UCLA_targeted_review_FY2025-26_exclusions_documentation_as_of_2026-07-09.xlsx
+++ b/output/Campus FY 2025-26 annual statistics NZ-level report/2025 - 2026/exclusions tab/UCLA_targeted_review_FY2025-26_exclusions_documentation_as_of_2026-07-09.xlsx
@@ -3634,7 +3634,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="55">
       <c r="A55" s="32" t="inlineStr">
         <is>
-          <t>"Portfolio Library Unit"."Library Name" is equal to / is in X_Do_Not_Use_</t>
+          <t>"Portfolio Library Unit"."Library Name" LIKE 'X_Do_Not_Use_%'</t>
         </is>
       </c>
       <c r="B55" s="39" t="inlineStr">
@@ -5711,7 +5711,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="86">
       <c r="A86" s="32" t="inlineStr">
         <is>
-          <t>"Electronic Collection"."Electronic Collection Public Name" is equal to / is in Ebook Central Perpetual, DDA and Subscription Titles; EBSCO (UCSD). eBook Collection DDA online monographs.; R2 Digital Library DDA</t>
+          <t>"Electronic Collection"."Electronic Collection Public Name" IN ('Ebook Central Perpetual, DDA and Subscription Titles', 'EBSCO (UCSD). eBook Collection DDA online monographs.', 'R2 Digital Library DDA')</t>
         </is>
       </c>
       <c r="B86" s="39" t="inlineStr">
@@ -5778,7 +5778,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="87">
       <c r="A87" s="32" t="inlineStr">
         <is>
-          <t>"Electronic Collection"."Electronic Collection Public Name" is equal to / is in British and Irish Women's Letters and Diaries: First Edition (Pre-January 2009 Purchasers Only); Books@Ovid - LWW JBIB Book Collection 2017-2018 Purchase; Books@Ovid Purchase; Books@Ovid Purchase Complete; North American Indian Drama: First Edition (Pre-October 2012 Purchasers Only); Twentieth Century North American Drama: First Edition (Pre-October 2012 Purchasers Only); Institute of Physics Historic Archive Purchase; Maruzen eBook Library; Berkeley LDC purchases; IGI Global Evidence Based PURCHASED; Oxford University Press Anthropology Local Purchased Collection; Sage EBS; Sage online monographs EBS (Sage EBS) purchased; UC Davis locally purchased monographs_LOCAL; UCSC owned streaming video; African Writers Series (pre-September 2011 purchase); SAGE Complete Deep Backfile Purchase 2008; SAGE Deep Backfile Upgrade Purchase 2009; SAGE Deep Backfile Upgrade Purchase 2010; SAGE Deep Backfile Upgrade Purchase 2011; SAGE Deep Backfile Upgrade Purchase 2012; SAGE Deep Backfile Upgrade Purchase 2013; SAGE Deep Backfile Upgrade Purchase 2014; SAGE Deep Backfile Upgrade Purchase 2015; SAGE Deep Backfile Upgrade Purchase 2016; SAGE Deep Backfile Upgrade Purchase 2017; SAGE Psychology Subject Collection Backfile Purchase; Taylor &amp; Francis online monographs (EBS) purchased</t>
+          <t>"Electronic Collection"."Electronic Collection Public Name" IN ('British and Irish Women''s Letters and Diaries: First Edition (Pre-January 2009 Purchasers Only)', 'Books@Ovid - LWW JBIB Book Collection 2017-2018 Purchase', 'Books@Ovid Purchase', 'Books@Ovid Purchase Complete', 'North American Indian Drama: First Edition (Pre-October 2012 Purchasers Only)', 'Twentieth Century North American Drama: First Edition (Pre-October 2012 Purchasers Only)', 'Institute of Physics Historic Archive Purchase', 'Maruzen eBook Library', 'Berkeley LDC purchases', 'IGI Global Evidence Based PURCHASED', 'Oxford University Press Anthropology Local Purchased Collection', 'Sage EBS', 'Sage online monographs EBS (Sage EBS) purchased', 'UC Davis locally purchased monographs_LOCAL', 'UCSC owned streaming video', 'African Writers Series (pre-September 2011 purchase)', 'SAGE Complete Deep Backfile Purchase 2008', 'SAGE Deep Backfile Upgrade Purchase 2009', 'SAGE Deep Backfile Upgrade Purchase 2010', 'SAGE Deep Backfile Upgrade Purchase 2011', 'SAGE Deep Backfile Upgrade Purchase 2012', 'SAGE Deep Backfile Upgrade Purchase 2013', 'SAGE Deep Backfile Upgrade Purchase 2014', 'SAGE Deep Backfile Upgrade Purchase 2015', 'SAGE Deep Backfile Upgrade Purchase 2016', 'SAGE Deep Backfile Upgrade Purchase 2017', 'SAGE Psychology Subject Collection Backfile Purchase', 'Taylor &amp; Francis online monographs (EBS) purchased')</t>
         </is>
       </c>
       <c r="B87" s="39" t="inlineStr">
@@ -5845,7 +5845,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="88">
       <c r="A88" s="32" t="inlineStr">
         <is>
-          <t>"Electronic Collection"."Electronic Collection Public Name"</t>
+          <t>"Electronic Collection"."Electronic Collection Public Name" IS NULL</t>
         </is>
       </c>
       <c r="B88" s="39" t="inlineStr">
@@ -6448,7 +6448,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="97">
       <c r="A97" s="32" t="inlineStr">
         <is>
-          <t>"Institution"."Institution Name"6533</t>
+          <t>"Institution"."Institution Name" = 6533</t>
         </is>
       </c>
       <c r="B97" s="39" t="inlineStr">
@@ -10401,7 +10401,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="156">
       <c r="A156" s="32" t="inlineStr">
         <is>
-          <t>"Item Location at Time of Loan"."Location Code" is equal to / is in 5542561600006533; arcgabx; uechlt; uerf; yrcleanup; yrcatsup; yrgic</t>
+          <t>"Item Location at Time of Loan"."Location Code" IN ('5542561600006533', 'arcgabx', 'uechlt', 'uerf', 'yrcleanup', 'yrcatsup', 'yrgic')</t>
         </is>
       </c>
       <c r="B156" s="39" t="inlineStr">
@@ -10468,7 +10468,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="157">
       <c r="A157" s="32" t="inlineStr">
         <is>
-          <t>"Item Location at Time of Loan"."Location Code" is equal to / is in archrome; arpubcirc; artclicc; bichrome; bioclicc; bipubcirc; boechrome; boeclicc; boepubcirc; cccollege; classclicc; clchrome; clicclocke; cliccpnloc; cliccpsloc; cliccynloc; cliccysloc; mgpubcirc; muchrome; musicclicc; sgclicc; UNASSIGNED; yrchrome; cliccpksk; cliccyksk; mgchrome; clpubcirc; yrpubcirc</t>
+          <t>"Item Location at Time of Loan"."Location Code" IN ('archrome', 'arpubcirc', 'artclicc', 'bichrome', 'bioclicc', 'bipubcirc', 'boechrome', 'boeclicc', 'boepubcirc', 'cccollege', 'classclicc', 'clchrome', 'clicclocke', 'cliccpnloc', 'cliccpsloc', 'cliccynloc', 'cliccysloc', 'mgpubcirc', 'muchrome', 'musicclicc', 'sgclicc', 'UNASSIGNED', 'yrchrome', 'cliccpksk', 'cliccyksk', 'mgchrome', 'clpubcirc', 'yrpubcirc')</t>
         </is>
       </c>
       <c r="B157" s="39" t="inlineStr">
@@ -10602,7 +10602,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="159">
       <c r="A159" s="32" t="inlineStr">
         <is>
-          <t>"Item Location at Time of Loan"."Location Code" is equal to / is in lwill; OUT_RS_REQ</t>
+          <t>"Item Location at Time of Loan"."Location Code" IN ('lwill', 'OUT_RS_REQ')</t>
         </is>
       </c>
       <c r="B159" s="39" t="inlineStr">
@@ -10669,7 +10669,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="160">
       <c r="A160" s="32" t="inlineStr">
         <is>
-          <t>"Item Location at Time of Loan"."Location Code" is equal to / is in arcr; birs; birsprscp; clrs; ears; lwrs; lwrsper; mgcirs; mgrs; mgrsstrg; murs; smcrs; yrcipr; yrrs</t>
+          <t>"Item Location at Time of Loan"."Location Code" IN ('arcr', 'birs', 'birsprscp', 'clrs', 'ears', 'lwrs', 'lwrsper', 'mgcirs', 'mgrs', 'mgrsstrg', 'murs', 'smcrs', 'yrcipr', 'yrrs')</t>
         </is>
       </c>
       <c r="B160" s="39" t="inlineStr">
@@ -10736,7 +10736,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="161">
       <c r="A161" s="32" t="inlineStr">
         <is>
-          <t>"Item Location at Time of Loan"."Location Code" is equal to / is in ar; arcg; arcgab; arcgabxx; arcgx; arcotf; armedia; arper; arperx; arplay; arrf; arrs; arscript; artsTS; arx; arxx-xxx; bi; bicidperm; bicotf; biper; birf; birsclas; cl; clcareer; clcook; cldisp; clenig; clgrfn; clnrfc; clof; clperm; clsustain; cltrav; clvidgames; clzine; ea; eadiujnl; eaover; eax; eaxx; herb; lsbihi; lsbirfhist; lsyrstax; lw; lwcivideo; lwcix; lwcleanup; lwofrf; lwphil; lwrf; lwsuper; lwtrr; lwwilliams; mgcleanup; mgnbks; mgrf; mgsccohi; mu; muclsd; muclsdmm; muclsdsdr; mumini; munbks; mux; muxx; muxxx; sg; sgan; sgcotf; sgdisp; sgmi; sgper; sgput; sm; smav; smcotf; smper; smrsperm; smsctallm; sr; srar; srar2; srbi2; srbuo; srca; srck; srcr; sret; sril; srmnm; srnoncirc; srub; srucl; srucl2; srucl3; srucl4; srud0; srud2; srui2; srur; sryr2; sryr7; sryr8; ue123e; ueabce; ueaubks; uebiog; ueefolk; ueestax; uefic; ueficer; uefolk; uefor; uenfic; uepap; uepoe; uesmalle; uesx; yr; yralmi; yran; yranx; yrci; yrlcotf; yrllost; yrmiclsd; yrpe; yrper; yrrisatl; yrrisrr; yrx; yrxx; yrxxx; arts; bix; ca; earf; clgame; sryr9</t>
+          <t>"Item Location at Time of Loan"."Location Code" IN ('ar', 'arcg', 'arcgab', 'arcgabxx', 'arcgx', 'arcotf', 'armedia', 'arper', 'arperx', 'arplay', 'arrf', 'arrs', 'arscript', 'artsTS', 'arx', 'arxx-xxx', 'bi', 'bicidperm', 'bicotf', 'biper', 'birf', 'birsclas', 'cl', 'clcareer', 'clcook', 'cldisp', 'clenig', 'clgrfn', 'clnrfc', 'clof', 'clperm', 'clsustain', 'cltrav', 'clvidgames', 'clzine', 'ea', 'eadiujnl', 'eaover', 'eax', 'eaxx', 'herb', 'lsbihi', 'lsbirfhist', 'lsyrstax', 'lw', 'lwcivideo', 'lwcix', 'lwcleanup', 'lwofrf', 'lwphil', 'lwrf', 'lwsuper', 'lwtrr', 'lwwilliams', 'mgcleanup', 'mgnbks', 'mgrf', 'mgsccohi', 'mu', 'muclsd', 'muclsdmm', 'muclsdsdr', 'mumini', 'munbks', 'mux', 'muxx', 'muxxx', 'sg', 'sgan', 'sgcotf', 'sgdisp', 'sgmi', 'sgper', 'sgput', 'sm', 'smav', 'smcotf', 'smper', 'smrsperm', 'smsctallm', 'sr', 'srar', 'srar2', 'srbi2', 'srbuo', 'srca', 'srck', 'srcr', 'sret', 'sril', 'srmnm', 'srnoncirc', 'srub', 'srucl', 'srucl2', 'srucl3', 'srucl4', 'srud0', 'srud2', 'srui2', 'srur', 'sryr2', 'sryr7', 'sryr8', 'ue123e', 'ueabce', 'ueaubks', 'uebiog', 'ueefolk', 'ueestax', 'uefic', 'ueficer', 'uefolk', 'uefor', 'uenfic', 'uepap', 'uepoe', 'uesmalle', 'uesx', 'yr', 'yralmi', 'yran', 'yranx', 'yrci', 'yrlcotf', 'yrllost', 'yrmiclsd', 'yrpe', 'yrper', 'yrrisatl', 'yrrisrr', 'yrx', 'yrxx', 'yrxxx', 'arts', 'bix', 'ca', 'earf', 'clgame', 'sryr9')</t>
         </is>
       </c>
       <c r="B161" s="39" t="inlineStr">
@@ -10937,7 +10937,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="164">
       <c r="A164" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group" is equal to / is in UCLA Acad - NoLimit; UCLA Acad Proxy; UCLA Academic; UCLA Law Academic; UCLA Law Proxy; UCLA Retired Academic</t>
+          <t>"Borrower Details"."User Group" IN ('UCLA Acad - NoLimit', 'UCLA Acad Proxy', 'UCLA Academic', 'UCLA Law Academic', 'UCLA Law Proxy', 'UCLA Retired Academic')</t>
         </is>
       </c>
       <c r="B164" s="39" t="inlineStr">
@@ -11004,7 +11004,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="165">
       <c r="A165" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group" is equal to / is in UCLA Graduate; UCLA Law Grad; UCLA Mgmt PhD; UCLA Music Grad; UCLA Grad NoLimit</t>
+          <t>"Borrower Details"."User Group" IN ('UCLA Graduate', 'UCLA Law Grad', 'UCLA Mgmt PhD', 'UCLA Music Grad', 'UCLA Grad NoLimit')</t>
         </is>
       </c>
       <c r="B165" s="39" t="inlineStr">
@@ -11071,7 +11071,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="166">
       <c r="A166" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group" is equal to / is in Internal Use Only; UCLA Law Staff; UCLA Lib Staff Recall; UCLA Staff</t>
+          <t>"Borrower Details"."User Group" IN ('Internal Use Only', 'UCLA Law Staff', 'UCLA Lib Staff Recall', 'UCLA Staff')</t>
         </is>
       </c>
       <c r="B166" s="39" t="inlineStr">
@@ -11138,7 +11138,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="167">
       <c r="A167" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group" is equal to / is in UCLA Music Undergrad; UCLA Undergrad</t>
+          <t>"Borrower Details"."User Group" IN ('UCLA Music Undergrad', 'UCLA Undergrad')</t>
         </is>
       </c>
       <c r="B167" s="39" t="inlineStr">
@@ -11205,7 +11205,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="168">
       <c r="A168" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group" is equal to / is in Early Childhood; Extension; External 10 - Associates; External 10 - UCLA Alumni; Geffen Academy Student; Lab School Parent; Lab School Student; SPR; UCLA Retired Staff; VGR</t>
+          <t>"Borrower Details"."User Group" IN ('Early Childhood', 'Extension', 'External 10 - Associates', 'External 10 - UCLA Alumni', 'Geffen Academy Student', 'Lab School Parent', 'Lab School Student', 'SPR', 'UCLA Retired Staff', 'VGR')</t>
         </is>
       </c>
       <c r="B168" s="39" t="inlineStr">
@@ -11272,7 +11272,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="169">
       <c r="A169" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group" is equal to / is in Access Only; AP/TAP Student; External 10; External 20; External 200 - Faculty; External 200 - Other; External 5 - Other; External 50 - Corporation</t>
+          <t>"Borrower Details"."User Group" IN ('Access Only', 'AP/TAP Student', 'External 10', 'External 20', 'External 200 - Faculty', 'External 200 - Other', 'External 5 - Other', 'External 50 - Corporation')</t>
         </is>
       </c>
       <c r="B169" s="39" t="inlineStr">
@@ -11339,7 +11339,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="170">
       <c r="A170" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group" is equal to / is in NETWORK; Network</t>
+          <t>"Borrower Details"."User Group" IN ('NETWORK', 'Network')</t>
         </is>
       </c>
       <c r="B170" s="39" t="inlineStr">
@@ -11406,7 +11406,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="171">
       <c r="A171" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group" is equal to / is in ILL Department - Non UC; ILL Department - UC</t>
+          <t>"Borrower Details"."User Group" IN ('ILL Department - Non UC', 'ILL Department - UC')</t>
         </is>
       </c>
       <c r="B171" s="39" t="inlineStr">
@@ -11473,7 +11473,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="172">
       <c r="A172" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group"</t>
+          <t>"Borrower Details"."User Group" IS NULL</t>
         </is>
       </c>
       <c r="B172" s="39" t="inlineStr">
@@ -11540,7 +11540,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="173">
       <c r="A173" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group" is equal to / is in EHS; UCLA Library Staff Department; Users to Purge</t>
+          <t>"Borrower Details"."User Group" IN ('EHS', 'UCLA Library Staff Department', 'Users to Purge')</t>
         </is>
       </c>
       <c r="B173" s="39" t="inlineStr">
